--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487991_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487991_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. MORTELLARO</t>
+          <t>P. LOPEZ GOMEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.266500000000001</v>
+        <v>8.8393</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8264</v>
+        <v>9.5282</v>
       </c>
       <c r="F2" t="n">
-        <v>2.44</v>
+        <v>-0.6889</v>
       </c>
       <c r="G2" t="n">
-        <v>4.1829</v>
+        <v>4.2821</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1354</v>
+        <v>-0.4931</v>
       </c>
       <c r="I2" t="n">
-        <v>3.0475</v>
+        <v>4.7752</v>
       </c>
       <c r="J2" t="n">
-        <v>4.9458</v>
+        <v>5.9142</v>
       </c>
       <c r="K2" t="n">
-        <v>2.3343</v>
+        <v>1.575</v>
       </c>
       <c r="L2" t="n">
-        <v>2.6115</v>
+        <v>4.3392</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7629</v>
+        <v>-1.632</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.1989</v>
+        <v>-2.068</v>
       </c>
       <c r="O2" t="n">
         <v>0.436</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3964</v>
+        <v>1.3876</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3787</v>
+        <v>3.3698</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2025</v>
+        <v>-0.1147</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0522</v>
+        <v>0.5012</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1503</v>
+        <v>-0.616</v>
       </c>
       <c r="V2" t="n">
-        <v>2.4846</v>
+        <v>3.2843</v>
       </c>
       <c r="W2" t="n">
-        <v>1.8107</v>
+        <v>5.095</v>
       </c>
       <c r="X2" t="n">
-        <v>0.674</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. LOPEZ GOMEZ</t>
+          <t>C. MORTELLARO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.129200000000001</v>
+        <v>8.1937</v>
       </c>
       <c r="E3" t="n">
-        <v>10.0146</v>
+        <v>6.0344</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8854</v>
+        <v>2.1593</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2821</v>
+        <v>4.1829</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4931</v>
+        <v>1.1354</v>
       </c>
       <c r="I3" t="n">
-        <v>4.7752</v>
+        <v>3.0475</v>
       </c>
       <c r="J3" t="n">
-        <v>5.9142</v>
+        <v>4.9458</v>
       </c>
       <c r="K3" t="n">
-        <v>1.575</v>
+        <v>2.3343</v>
       </c>
       <c r="L3" t="n">
-        <v>4.3392</v>
+        <v>2.6115</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.632</v>
+        <v>-0.7629</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.068</v>
+        <v>-1.1989</v>
       </c>
       <c r="O3" t="n">
         <v>0.436</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3876</v>
+        <v>0.3964</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R3" t="n">
-        <v>3.3698</v>
+        <v>2.3787</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1752</v>
+        <v>1.1297</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9877</v>
+        <v>1.2602</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8125</v>
+        <v>-0.1305</v>
       </c>
       <c r="V3" t="n">
-        <v>3.2843</v>
+        <v>2.4846</v>
       </c>
       <c r="W3" t="n">
-        <v>5.095</v>
+        <v>1.8107</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.8107</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. DIKE EGUN</t>
+          <t>H. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.6876</v>
+        <v>3.508</v>
       </c>
       <c r="E4" t="n">
-        <v>5.9864</v>
+        <v>2.8185</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2988</v>
+        <v>0.6895</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2407</v>
+        <v>-0.5813</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2894</v>
+        <v>-0.3115</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5301</v>
+        <v>-0.2698</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7397</v>
+        <v>1.5962</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6192</v>
+        <v>1.6286</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1205</v>
+        <v>-0.0324</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9804</v>
+        <v>-2.1775</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3298</v>
+        <v>-1.94</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6506</v>
+        <v>-0.2374</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7929</v>
+        <v>1.1893</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7929</v>
+        <v>3.1716</v>
       </c>
       <c r="S4" t="n">
-        <v>4.6023</v>
+        <v>0.6819</v>
       </c>
       <c r="T4" t="n">
-        <v>4.7136</v>
+        <v>0.7903</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1113</v>
+        <v>-0.1084</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5331</v>
+        <v>2.218</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5331</v>
+        <v>2.4142</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1962</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. VAZQUEZ GARCIA</t>
+          <t>K. DIKE EGUN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6368</v>
+        <v>3.2604</v>
       </c>
       <c r="E5" t="n">
-        <v>1.228</v>
+        <v>3.6434</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4087</v>
+        <v>-0.383</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5813</v>
+        <v>-0.2407</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3115</v>
+        <v>0.2894</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2698</v>
+        <v>-0.5301</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5962</v>
+        <v>0.7397</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6286</v>
+        <v>0.6192</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0324</v>
+        <v>0.1205</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.1775</v>
+        <v>-0.9804</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.94</v>
+        <v>-0.3298</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2374</v>
+        <v>-0.6506</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1893</v>
+        <v>0.7929</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.1716</v>
+        <v>0.7929</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1893</v>
+        <v>2.175</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8001</v>
+        <v>2.3706</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3892</v>
+        <v>-0.1956</v>
       </c>
       <c r="V5" t="n">
-        <v>2.218</v>
+        <v>0.5331</v>
       </c>
       <c r="W5" t="n">
-        <v>2.4142</v>
+        <v>0.5331</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1962</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1364</v>
+        <v>0.5325</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8638</v>
+        <v>2.2318</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7274</v>
+        <v>-1.6993</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0181</v>
@@ -1000,13 +1000,13 @@
         <v>0.3964</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2419</v>
+        <v>0.1542</v>
       </c>
       <c r="T7" t="n">
-        <v>0.011</v>
+        <v>0.379</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2529</v>
+        <v>-0.2249</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BUZZO</t>
+          <t>J. AGUERA ZEA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.4158</v>
+        <v>-2.2558</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.5314</v>
+        <v>-1.0791</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1156</v>
+        <v>-1.1767</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.599</v>
+        <v>-4.1304</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.898</v>
+        <v>-1.6088</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.7009</v>
+        <v>-2.5216</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.5049</v>
+        <v>-2.3604</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3718</v>
+        <v>0.1954</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.8767</v>
+        <v>-2.5558</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0941</v>
+        <v>-1.77</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.2698</v>
+        <v>-1.8042</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1757</v>
+        <v>0.0342</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.3876</v>
+        <v>1.1893</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.9556</v>
+        <v>-0.9911</v>
       </c>
       <c r="R8" t="n">
-        <v>3.568</v>
+        <v>2.1805</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0589</v>
+        <v>0.4618</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9082</v>
+        <v>-0.3801</v>
       </c>
       <c r="V8" t="n">
         <v>0.6036</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8701</v>
+        <v>1.8107</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2666</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7716</v>
+        <v>-3.2175</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3835</v>
+        <v>-0.9136</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3881</v>
+        <v>-2.3039</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8864</v>
@@ -1156,13 +1156,13 @@
         <v>1.5858</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7991</v>
+        <v>-0.245</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4881</v>
+        <v>-0.0183</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.311</v>
+        <v>-0.2267</v>
       </c>
       <c r="V9" t="n">
         <v>-2.6808</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. DIMITROV KOLEV</t>
+          <t>A. BUZZO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.889</v>
+        <v>-3.2799</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0201</v>
+        <v>-4.6935</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.9091</v>
+        <v>1.4136</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8452</v>
+        <v>-3.599</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8273</v>
+        <v>-1.898</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0179</v>
+        <v>-1.7009</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5515</v>
+        <v>-1.5049</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5114</v>
+        <v>0.3718</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0402</v>
+        <v>-1.8767</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.3967</v>
+        <v>-2.0941</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3386</v>
+        <v>-2.2698</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0581</v>
+        <v>0.1757</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3964</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9911</v>
+        <v>-4.9556</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3876</v>
+        <v>3.568</v>
       </c>
       <c r="S10" t="n">
-        <v>0.311</v>
+        <v>1.1031</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7967</v>
+        <v>0.8968</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4857</v>
+        <v>0.2062</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.7512</v>
+        <v>0.6036</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.337</v>
+        <v>0.8701</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.4142</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. AGUERA ZEA</t>
+          <t>I. DIMITROV KOLEV</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9233</v>
+        <v>-4.0999</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4658</v>
+        <v>-0.3874</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4575</v>
+        <v>-3.7125</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.1304</v>
+        <v>-1.8452</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6088</v>
+        <v>-0.8273</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.5216</v>
+        <v>-1.0179</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.3604</v>
+        <v>0.5515</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1954</v>
+        <v>0.5114</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.5558</v>
+        <v>0.0402</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.77</v>
+        <v>-2.3967</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.8042</v>
+        <v>-1.3386</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0342</v>
+        <v>-1.0581</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1893</v>
+        <v>0.3964</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1805</v>
+        <v>1.3876</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5858</v>
+        <v>0.1001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9249000000000001</v>
+        <v>0.3892</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6609</v>
+        <v>-0.2891</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6036</v>
+        <v>-2.7512</v>
       </c>
       <c r="W11" t="n">
-        <v>1.8107</v>
+        <v>-0.337</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2071</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="12">
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>12.3701</v>
+        <v>12.9941</v>
       </c>
       <c r="E12" t="n">
-        <v>18.0719</v>
+        <v>18.696</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.702</v>
+        <v>-5.701899999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-1.322800000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.7951</v>
+        <v>-2.795100000000001</v>
       </c>
       <c r="I12" t="n">
         <v>1.472399999999999</v>
@@ -1366,7 +1366,7 @@
         <v>12.1369</v>
       </c>
       <c r="K12" t="n">
-        <v>8.883899999999999</v>
+        <v>8.883900000000001</v>
       </c>
       <c r="L12" t="n">
         <v>3.253099999999999</v>
@@ -1390,13 +1390,13 @@
         <v>18.8313</v>
       </c>
       <c r="S12" t="n">
-        <v>4.442099999999999</v>
+        <v>5.066</v>
       </c>
       <c r="T12" t="n">
-        <v>6.407000000000001</v>
+        <v>7.030799999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.965</v>
+        <v>-1.9651</v>
       </c>
       <c r="V12" t="n">
         <v>4.2952</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V. PALOMO GIL</t>
+          <t>E. TRUJILLO MARIN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.5131</v>
+        <v>3.8035</v>
       </c>
       <c r="E13" t="n">
-        <v>4.1461</v>
+        <v>5.3374</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.633</v>
+        <v>-1.5339</v>
       </c>
       <c r="G13" t="n">
-        <v>5.5416</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>6.0085</v>
+        <v>-2.4518</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4668</v>
+        <v>1.7678</v>
       </c>
       <c r="J13" t="n">
-        <v>7.6603</v>
+        <v>1.8461</v>
       </c>
       <c r="K13" t="n">
-        <v>8.138500000000001</v>
+        <v>-0.0462</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.4782</v>
+        <v>1.8922</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.1186</v>
+        <v>-2.53</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.13</v>
+        <v>-2.4056</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0114</v>
+        <v>-0.1244</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.5769</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.9556</v>
+        <v>-2.9733</v>
       </c>
       <c r="R13" t="n">
         <v>2.3787</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8149999999999999</v>
+        <v>-0.0128</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1749</v>
+        <v>0.1625</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3599</v>
+        <v>-0.1754</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2666</v>
+        <v>5.095</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2666</v>
+        <v>6.3021</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5331</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1331</v>
+        <v>2.9796</v>
       </c>
       <c r="E14" t="n">
-        <v>4.7376</v>
+        <v>4.2283</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6045</v>
+        <v>-1.2486</v>
       </c>
       <c r="G14" t="n">
         <v>4.3257</v>
@@ -1546,13 +1546,13 @@
         <v>1.1893</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5385</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.1112</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.159</v>
+        <v>-0.8031</v>
       </c>
       <c r="V14" t="n">
         <v>0.337</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. TRUJILLO MARIN</t>
+          <t>V. PALOMO GIL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7581</v>
+        <v>2.9019</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6243</v>
+        <v>3.5349</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.8662</v>
+        <v>-0.633</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6840000000000001</v>
+        <v>5.5416</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.4518</v>
+        <v>6.0085</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7678</v>
+        <v>-0.4668</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8461</v>
+        <v>7.6603</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0462</v>
+        <v>8.138500000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>1.8922</v>
+        <v>-0.4782</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.53</v>
+        <v>-2.1186</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.4056</v>
+        <v>-2.13</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1244</v>
+        <v>0.0114</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.5947</v>
+        <v>-2.5769</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9733</v>
+        <v>-4.9556</v>
       </c>
       <c r="R15" t="n">
         <v>2.3787</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0583</v>
+        <v>0.2037</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5505</v>
+        <v>0.5636</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5078</v>
+        <v>-0.3599</v>
       </c>
       <c r="V15" t="n">
-        <v>5.095</v>
+        <v>-0.2666</v>
       </c>
       <c r="W15" t="n">
-        <v>6.3021</v>
+        <v>0.2666</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2071</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4183</v>
+        <v>0.903</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6921</v>
+        <v>0.8772</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2739</v>
+        <v>0.0258</v>
       </c>
       <c r="G16" t="n">
         <v>1.1389</v>
@@ -1702,13 +1702,13 @@
         <v>0.3964</v>
       </c>
       <c r="S16" t="n">
-        <v>0.08110000000000001</v>
+        <v>-0.4341</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0463</v>
+        <v>0.2313</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9651999999999999</v>
+        <v>-0.6654</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. VAZQUEZ GARCIA</t>
+          <t>I. MARTIN ARROYO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1538</v>
+        <v>-0.155</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5522</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3984</v>
+        <v>-0.155</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0528</v>
+        <v>-0.2018</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.7166</v>
+        <v>-0.2018</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6637999999999999</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.817</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4912</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3259</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.8698</v>
+        <v>-0.2018</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.2078</v>
+        <v>-0.2018</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.662</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5947</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2858</v>
+        <v>0.0468</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7967</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4891</v>
+        <v>0.0468</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.0704</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. MARTIN ARROYO</t>
+          <t>A. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1831</v>
+        <v>-0.5273</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1.3485</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1831</v>
+        <v>-1.8758</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2018</v>
+        <v>-1.0528</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2018</v>
+        <v>-1.7166</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1.817</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.4912</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.3259</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2018</v>
+        <v>-2.8698</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2018</v>
+        <v>-2.2078</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-0.662</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.5947</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0187</v>
+        <v>0.6048</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.5929</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0187</v>
+        <v>0.0118</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.0704</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. PARRA MENDIVIL</t>
+          <t>O. DIAZ GUILLEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2051</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>4.2093</v>
+        <v>0.1604</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.4144</v>
+        <v>-0.7214</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5153</v>
+        <v>0.0312</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0153</v>
+        <v>0.9493</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5306</v>
+        <v>-0.9181</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5595</v>
+        <v>1.8956</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1009</v>
+        <v>2.6836</v>
       </c>
       <c r="L19" t="n">
-        <v>2.4586</v>
+        <v>-0.788</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0442</v>
+        <v>-1.8645</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1162</v>
+        <v>-1.7343</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.928</v>
+        <v>-0.1301</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3964</v>
+        <v>0.1982</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3964</v>
+        <v>2.1805</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3062</v>
+        <v>0.4167</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0463</v>
+        <v>0.247</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.3525</v>
+        <v>0.1697</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8107</v>
+        <v>-1.2071</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.4142</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. DIAZ GUILLEN</t>
+          <t>T. PARRA MENDIVIL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1755</v>
+        <v>-0.7588</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1452</v>
+        <v>3.4962</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0303</v>
+        <v>-4.2551</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0312</v>
+        <v>1.5153</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9493</v>
+        <v>-0.0153</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9181</v>
+        <v>1.5306</v>
       </c>
       <c r="J20" t="n">
-        <v>1.8956</v>
+        <v>2.5595</v>
       </c>
       <c r="K20" t="n">
-        <v>2.6836</v>
+        <v>0.1009</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.788</v>
+        <v>2.4586</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8645</v>
+        <v>-1.0442</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7343</v>
+        <v>-0.1162</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1301</v>
+        <v>-0.928</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1982</v>
+        <v>0.3964</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1805</v>
+        <v>0.3964</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1978</v>
+        <v>-0.8599</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0586</v>
+        <v>0.3332</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1392</v>
+        <v>-1.1931</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2071</v>
+        <v>-1.8107</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2071</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8582</v>
+        <v>-2.1627</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.5451</v>
+        <v>-2.9339</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6869</v>
+        <v>0.7712</v>
       </c>
       <c r="G21" t="n">
         <v>-3.1581</v>
@@ -2092,13 +2092,13 @@
         <v>1.3876</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4137</v>
+        <v>0.2817</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4368</v>
+        <v>0.1744</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0231</v>
+        <v>0.1073</v>
       </c>
       <c r="V21" t="n">
         <v>-0.674</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2636</v>
+        <v>-2.5975</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4691</v>
+        <v>-1.1635</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7945</v>
+        <v>-1.434</v>
       </c>
       <c r="G22" t="n">
         <v>0.6555</v>
@@ -2170,13 +2170,13 @@
         <v>0.1982</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.3244</v>
+        <v>-1.6584</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5616</v>
+        <v>-0.256</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.7628</v>
+        <v>-1.4024</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6036</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1656</v>
+        <v>-4.6223</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9141</v>
+        <v>-2.5066</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2515</v>
+        <v>-2.1157</v>
       </c>
       <c r="G23" t="n">
         <v>-3.6223</v>
@@ -2248,13 +2248,13 @@
         <v>0.9911</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7415</v>
+        <v>-0.1982</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4368</v>
+        <v>-0.0293</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3047</v>
+        <v>-0.1689</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6036</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.4953</v>
+        <v>-10.2152</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.1861</v>
+        <v>-6.6768</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.3092</v>
+        <v>-3.5384</v>
       </c>
       <c r="G24" t="n">
         <v>-3.1666</v>
@@ -2326,13 +2326,13 @@
         <v>0.7929</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0621</v>
+        <v>-0.7819</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6753</v>
+        <v>-0.166</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3868</v>
+        <v>-0.616</v>
       </c>
       <c r="V24" t="n">
         <v>-3.8879</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-12.37</v>
+        <v>-11.0118</v>
       </c>
       <c r="E25" t="n">
-        <v>5.701999999999996</v>
+        <v>5.7021</v>
       </c>
       <c r="F25" t="n">
-        <v>-18.0721</v>
+        <v>-16.7139</v>
       </c>
       <c r="G25" t="n">
         <v>1.3226</v>
       </c>
       <c r="H25" t="n">
-        <v>2.7951</v>
+        <v>2.795099999999998</v>
       </c>
       <c r="I25" t="n">
         <v>-1.4723</v>
@@ -2404,13 +2404,13 @@
         <v>13.8756</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.4419</v>
+        <v>-3.083600000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>1.9651</v>
+        <v>1.9648</v>
       </c>
       <c r="U25" t="n">
-        <v>-6.407</v>
+        <v>-5.0486</v>
       </c>
       <c r="V25" t="n">
         <v>-4.295500000000001</v>
